--- a/data_out/country_spreadsheets/Serbia.xlsx
+++ b/data_out/country_spreadsheets/Serbia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>121.12</v>
       </c>
+      <c r="X2" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>110.04</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>246.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>218.68</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>138.48</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>111.66</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>121.41</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>118.12</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>121.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>193.31</v>
       </c>
+      <c r="X3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>298.64</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>139.73</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>167.79</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>112.79</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>193.31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>263.68</v>
       </c>
+      <c r="X4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>84.11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>169.41</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>149.36</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>130.64</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>104</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>210.83</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>263.68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>183.8</v>
       </c>
+      <c r="X5" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>310.61</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>150.58</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>165.98</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>191.86</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>183.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>220.5</v>
       </c>
+      <c r="X6" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>101.76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>315.57</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>157.41</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>193.34</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>155.89</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>220.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>181.24</v>
       </c>
+      <c r="X7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>277.69</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>116.38</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>170.57</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>181.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>225.53</v>
       </c>
+      <c r="X8" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>312.21</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>73.42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>113.82</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>166.96</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>149.39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>225.53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>128.81</v>
       </c>
+      <c r="X9" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>320.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>180.34</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>127.56</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>97.77</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>149.28</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>128.81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>113.1</v>
       </c>
+      <c r="X10" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>83.59</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>269.58</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>126.22</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>109.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>128.35</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120.19</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>177.94</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>127.32</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>113.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>112.76</v>
       </c>
+      <c r="X11" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>139.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>255.26</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>202.99</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>201.01</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>196.88</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>221.61</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>112.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>111.9</v>
       </c>
+      <c r="X12" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>272.76</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>127.47</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>136.27</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>141.51</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>144.87</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>219.99</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>111.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>117.91</v>
       </c>
+      <c r="X13" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>90.27</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>159.59</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>108.69</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>102.54</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>117.91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>179.11</v>
       </c>
+      <c r="X14" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>74.92</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>232.43</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>117.66</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>115.18</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>78.77</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>155.74</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>191.09</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>179.11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>142.15</v>
       </c>
+      <c r="X15" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>217.79</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>158.21</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>64.39</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>89.62</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>92.42</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>123.69</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>142.15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>141.5</v>
       </c>
+      <c r="X16" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>241.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>106.43</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>112.67</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>131.46</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>141.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="X17" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>133.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>243.41</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>109.11</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>133.95</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>166.27</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>89.98999999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>273.73</v>
       </c>
+      <c r="X18" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>286.01</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>162.67</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>252.75</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>115.39</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>151.31</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>134.14</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>255.52</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>273.73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>234.64</v>
       </c>
+      <c r="X19" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>232.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>133.35</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>143.41</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>89.87</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>174.11</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>153.93</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>234.64</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>218.33</v>
       </c>
+      <c r="X20" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>146.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>119.54</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>154.81</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>122.86</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>103.57</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>218.33</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>93.19</v>
       </c>
+      <c r="X21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>197.21</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>136.33</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>162.43</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>93.19</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>131.28</v>
       </c>
+      <c r="X22" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>167.27</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>73.98</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>144.93</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>164.62</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>131.28</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>114.29</v>
       </c>
+      <c r="X23" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>224.91</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>261.37</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>162.15</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>114.29</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>86.68000000000001</v>
       </c>
+      <c r="X24" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>86.12</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>213.44</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>112.99</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>101.94</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>156.08</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>86.68000000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>92.48999999999999</v>
       </c>
+      <c r="X25" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>232.84</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>134.24</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>65.89</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>163.54</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>92.48999999999999</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2467,6 +3776,57 @@
         <v>96.18000000000001</v>
       </c>
       <c r="W26" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="X26" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>202.96</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>132.83</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>135.03</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>115.91</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>96.18000000000001</v>
+      </c>
+      <c r="AN26" t="n">
         <v>158.64</v>
       </c>
     </row>
